--- a/EKG_Kalite_Yönetim_Sistemi/90_NSA, MPA ve PPQ Hazırlık Araçları/01_Kaynak Form, Kriter ve Kanıt Takibi/EKG-YNT-LST-11_surec_ve_kanit_sorumlusu_atama_listesi__iso_9001_icerig.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/90_NSA, MPA ve PPQ Hazırlık Araçları/01_Kaynak Form, Kriter ve Kanıt Takibi/EKG-YNT-LST-11_surec_ve_kanit_sorumlusu_atama_listesi__iso_9001_icerig.xlsx
@@ -828,7 +828,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-YNT-LST-11&amp;C&amp;"Arial,Regular"&amp;11Süreç ve Kanıt Sorumlusu Atama Listesi - ISO 9001 İçeriği</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 12.06.2026 | Revizyon: 28.09.2026
+Revizyon nedeni: Genel ISO9001 destek listesi olduğu açıklandı; rol, kanıt ve müşteri kriter eşleştirmesi alanı korundu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>